--- a/web/files/港岛-北角-柏蔚山.xlsx
+++ b/web/files/港岛-北角-柏蔚山.xlsx
@@ -38834,15 +38834,52 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3136呎 (4+房)
+$17716万
+$56,491/呎
+(21年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2334呎 (4+房)
+$8578万
+$36,752/呎
+(25年-12月-01日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 2375呎 (4+房)
+$11875万
+$50,000/呎
+(19年-11月-20日)</t>
+        </is>
+      </c>
       <c r="E6" s="20" t="inlineStr"/>
       <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
 $2809万
@@ -38850,7 +38887,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 615呎 (2房)
 $2371万
@@ -38858,7 +38895,7 @@
 (19年-05月-27日)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
 $2265万
@@ -38866,43 +38903,6 @@
 (19年-07月-09日)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3136呎 (4+房)
-$17716万
-$56,491/呎
-(21年-03月-23日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 2334呎 (4+房)
-$8578万
-$36,752/呎
-(25年-12月-01日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 2375呎 (4+房)
-$11875万
-$50,000/呎
-(19年-11月-20日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -40889,11 +40889,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2058呎 (4+房)
+$10496万
+$51,000/呎
+(20年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1856呎 (4+房)
+$9317万
+$50,200/呎
+(22年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 2028呎 (4+房)
+$10500万
+$51,774/呎
+(21年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1014呎 (4+房)
 $4398万
@@ -40901,10 +40937,10 @@
 (19年-10月-22日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 1048呎 (4+房)
 $4284万
@@ -40912,7 +40948,7 @@
 (20年-09月-29日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 1075呎 (4+房)
 $3477万
@@ -40920,42 +40956,6 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2058呎 (4+房)
-$10496万
-$51,000/呎
-(20年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1856呎 (4+房)
-$9317万
-$50,200/呎
-(22年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>E | 2028呎 (4+房)
-$10500万
-$51,774/呎
-(21年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -42764,11 +42764,48 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2503呎 (4+房)
+$12510万
+$49,980/呎
+(23年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1624呎 (4+房)
+$8206万
+$50,531/呎
+(20年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 2282呎 (4+房)
+$11684万
+$51,200/呎
+(20年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 662呎 (1房)
 $2895万
@@ -42776,10 +42813,10 @@
 (19年-05月-27日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 908呎 (3房)
 $2902万
@@ -42787,7 +42824,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
 $2840万
@@ -42795,7 +42832,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 834呎 (3房)
 $2659万
@@ -42803,43 +42840,6 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2503呎 (4+房)
-$12510万
-$49,980/呎
-(23年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1624呎 (4+房)
-$8206万
-$50,531/呎
-(20年-03月-23日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 2282呎 (4+房)
-$11684万
-$51,200/呎
-(20年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">

--- a/web/files/港岛-北角-柏蔚山.xlsx
+++ b/web/files/港岛-北角-柏蔚山.xlsx
@@ -38834,10 +38834,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 899呎 (3房)
+$2809万
+$31,244/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 615呎 (2房)
+$2371万
+$38,551/呎
+(19年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 617呎 (2房)
+$2265万
+$36,707/呎
+(19年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3136呎 (4+房)
 $17716万
@@ -38845,7 +38882,7 @@
 (21年-03月-23日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 2334呎 (4+房)
 $8578万
@@ -38853,7 +38890,7 @@
 (25年-12月-01日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 2375呎 (4+房)
 $11875万
@@ -38861,48 +38898,11 @@
 (19年-11月-20日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
       <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 899呎 (3房)
-$2809万
-$31,244/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 615呎 (2房)
-$2371万
-$38,551/呎
-(19年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>H | 617呎 (2房)
-$2265万
-$36,707/呎
-(19年-07月-09日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -40889,10 +40889,46 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1014呎 (4+房)
+$4398万
+$43,370/呎
+(19年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 1048呎 (4+房)
+$4284万
+$40,874/呎
+(20年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 1075呎 (4+房)
+$3477万
+$32,347/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2058呎 (4+房)
 $10496万
@@ -40900,8 +40936,8 @@
 (20年-04月-01日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1856呎 (4+房)
 $9317万
@@ -40909,8 +40945,8 @@
 (22年-07月-21日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 2028呎 (4+房)
 $10500万
@@ -40918,44 +40954,8 @@
 (21年-03月-10日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1014呎 (4+房)
-$4398万
-$43,370/呎
-(19年-10月-22日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 1048呎 (4+房)
-$4284万
-$40,874/呎
-(20年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 1075呎 (4+房)
-$3477万
-$32,347/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -42764,10 +42764,54 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 662呎 (1房)
+$2895万
+$43,731/呎
+(19年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 908呎 (3房)
+$2902万
+$31,961/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 908呎 (3房)
+$2840万
+$31,278/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 834呎 (3房)
+$2659万
+$31,880/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2503呎 (4+房)
 $12510万
@@ -42775,8 +42819,8 @@
 (23年-05月-22日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1624呎 (4+房)
 $8206万
@@ -42784,7 +42828,7 @@
 (20年-03月-23日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 2282呎 (4+房)
 $11684万
@@ -42792,54 +42836,10 @@
 (20年-04月-22日)</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 662呎 (1房)
-$2895万
-$43,731/呎
-(19年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 908呎 (3房)
-$2902万
-$31,961/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 908呎 (3房)
-$2840万
-$31,278/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>H | 834呎 (3房)
-$2659万
-$31,880/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">

--- a/web/files/港岛-北角-柏蔚山.xlsx
+++ b/web/files/港岛-北角-柏蔚山.xlsx
@@ -16215,38 +16215,30 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H252" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I252" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H252" s="5" t="n">
+        <v>34117000</v>
+      </c>
+      <c r="I252" s="5" t="n">
+        <v>26843</v>
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K252" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L252" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K252" s="5" t="n">
+        <v>34117000</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>26843</v>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
@@ -16255,7 +16247,7 @@
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38834,15 +38826,52 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3136呎 (4+房)
+$17716万
+$56,491/呎
+(21年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2334呎 (4+房)
+$8578万
+$36,752/呎
+(25年-12月-01日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 2375呎 (4+房)
+$11875万
+$50,000/呎
+(19年-11月-20日)</t>
+        </is>
+      </c>
       <c r="E6" s="20" t="inlineStr"/>
       <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
 $2809万
@@ -38850,7 +38879,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 615呎 (2房)
 $2371万
@@ -38858,7 +38887,7 @@
 (19年-05月-27日)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
 $2265万
@@ -38866,43 +38895,6 @@
 (19年-07月-09日)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3136呎 (4+房)
-$17716万
-$56,491/呎
-(21年-03月-23日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 2334呎 (4+房)
-$8578万
-$36,752/呎
-(25年-12月-01日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 2375呎 (4+房)
-$11875万
-$50,000/呎
-(19年-11月-20日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -40779,7 +40771,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40789,7 +40781,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40889,11 +40881,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2058呎 (4+房)
+$10496万
+$51,000/呎
+(20年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1856呎 (4+房)
+$9317万
+$50,200/呎
+(22年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 2028呎 (4+房)
+$10500万
+$51,774/呎
+(21年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1014呎 (4+房)
 $4398万
@@ -40901,10 +40929,10 @@
 (19年-10月-22日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 1048呎 (4+房)
 $4284万
@@ -40912,7 +40940,7 @@
 (20年-09月-29日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 1075呎 (4+房)
 $3477万
@@ -40920,42 +40948,6 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2058呎 (4+房)
-$10496万
-$51,000/呎
-(20年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1856呎 (4+房)
-$9317万
-$50,200/呎
-(22年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>E | 2028呎 (4+房)
-$10500万
-$51,774/呎
-(21年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -41192,12 +41184,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 1271呎 (4+房)
-招标单位
--
-(在售)</t>
+$3412万
+$26,843/呎
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -42764,11 +42756,48 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2503呎 (4+房)
+$12510万
+$49,980/呎
+(23年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1624呎 (4+房)
+$8206万
+$50,531/呎
+(20年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 2282呎 (4+房)
+$11684万
+$51,200/呎
+(20年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 662呎 (1房)
 $2895万
@@ -42776,10 +42805,10 @@
 (19年-05月-27日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 908呎 (3房)
 $2902万
@@ -42787,7 +42816,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
 $2840万
@@ -42795,7 +42824,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 834呎 (3房)
 $2659万
@@ -42803,43 +42832,6 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2503呎 (4+房)
-$12510万
-$49,980/呎
-(23年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1624呎 (4+房)
-$8206万
-$50,531/呎
-(20年-03月-23日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 2282呎 (4+房)
-$11684万
-$51,200/呎
-(20年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">

--- a/web/files/港岛-北角-柏蔚山.xlsx
+++ b/web/files/港岛-北角-柏蔚山.xlsx
@@ -15091,38 +15091,30 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H234" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I234" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>36943000</v>
+      </c>
+      <c r="I234" s="5" t="n">
+        <v>29066</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K234" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L234" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K234" s="5" t="n">
+        <v>36943000</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>29066</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
@@ -15131,7 +15123,7 @@
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38826,10 +38818,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 899呎 (3房)
+$2809万
+$31,244/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 615呎 (2房)
+$2371万
+$38,551/呎
+(19年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 617呎 (2房)
+$2265万
+$36,707/呎
+(19年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3136呎 (4+房)
 $17716万
@@ -38837,7 +38866,7 @@
 (21年-03月-23日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 2334呎 (4+房)
 $8578万
@@ -38845,7 +38874,7 @@
 (25年-12月-01日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 2375呎 (4+房)
 $11875万
@@ -38853,48 +38882,11 @@
 (19年-11月-20日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
       <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 899呎 (3房)
-$2809万
-$31,244/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 615呎 (2房)
-$2371万
-$38,551/呎
-(19年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>H | 617呎 (2房)
-$2265万
-$36,707/呎
-(19年-07月-09日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -40771,7 +40763,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40781,7 +40773,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>186</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40881,10 +40873,46 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1014呎 (4+房)
+$4398万
+$43,370/呎
+(19年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 1048呎 (4+房)
+$4284万
+$40,874/呎
+(20年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 1075呎 (4+房)
+$3477万
+$32,347/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2058呎 (4+房)
 $10496万
@@ -40892,8 +40920,8 @@
 (20年-04月-01日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1856呎 (4+房)
 $9317万
@@ -40901,8 +40929,8 @@
 (22年-07月-21日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 2028呎 (4+房)
 $10500万
@@ -40910,44 +40938,8 @@
 (21年-03月-10日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1014呎 (4+房)
-$4398万
-$43,370/呎
-(19年-10月-22日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 1048呎 (4+房)
-$4284万
-$40,874/呎
-(20年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 1075呎 (4+房)
-$3477万
-$32,347/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -41013,12 +41005,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 1271呎 (4+房)
-招标单位
--
-(在售)</t>
+$3694万
+$29,066/呎
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -42756,10 +42748,54 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 662呎 (1房)
+$2895万
+$43,731/呎
+(19年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 908呎 (3房)
+$2902万
+$31,961/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 908呎 (3房)
+$2840万
+$31,278/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 834呎 (3房)
+$2659万
+$31,880/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2503呎 (4+房)
 $12510万
@@ -42767,8 +42803,8 @@
 (23年-05月-22日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1624呎 (4+房)
 $8206万
@@ -42776,7 +42812,7 @@
 (20年-03月-23日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 2282呎 (4+房)
 $11684万
@@ -42784,54 +42820,10 @@
 (20年-04月-22日)</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 662呎 (1房)
-$2895万
-$43,731/呎
-(19年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 908呎 (3房)
-$2902万
-$31,961/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 908呎 (3房)
-$2840万
-$31,278/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>H | 834呎 (3房)
-$2659万
-$31,880/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">

--- a/web/files/港岛-北角-柏蔚山.xlsx
+++ b/web/files/港岛-北角-柏蔚山.xlsx
@@ -38818,15 +38818,52 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3136呎 (4+房)
+$17716万
+$56,491/呎
+(21年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2334呎 (4+房)
+$8578万
+$36,752/呎
+(25年-12月-01日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 2375呎 (4+房)
+$11875万
+$50,000/呎
+(19年-11月-20日)</t>
+        </is>
+      </c>
       <c r="E6" s="20" t="inlineStr"/>
       <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
 $2809万
@@ -38834,7 +38871,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 615呎 (2房)
 $2371万
@@ -38842,7 +38879,7 @@
 (19年-05月-27日)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
 $2265万
@@ -38850,43 +38887,6 @@
 (19年-07月-09日)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 3136呎 (4+房)
-$17716万
-$56,491/呎
-(21年-03月-23日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 2334呎 (4+房)
-$8578万
-$36,752/呎
-(25年-12月-01日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 2375呎 (4+房)
-$11875万
-$50,000/呎
-(19年-11月-20日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -40873,11 +40873,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2058呎 (4+房)
+$10496万
+$51,000/呎
+(20年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1856呎 (4+房)
+$9317万
+$50,200/呎
+(22年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 2028呎 (4+房)
+$10500万
+$51,774/呎
+(21年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1014呎 (4+房)
 $4398万
@@ -40885,10 +40921,10 @@
 (19年-10月-22日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 1048呎 (4+房)
 $4284万
@@ -40896,7 +40932,7 @@
 (20年-09月-29日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 1075呎 (4+房)
 $3477万
@@ -40904,42 +40940,6 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2058呎 (4+房)
-$10496万
-$51,000/呎
-(20年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1856呎 (4+房)
-$9317万
-$50,200/呎
-(22年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>E | 2028呎 (4+房)
-$10500万
-$51,774/呎
-(21年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -42748,11 +42748,48 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2503呎 (4+房)
+$12510万
+$49,980/呎
+(23年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1624呎 (4+房)
+$8206万
+$50,531/呎
+(20年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 2282呎 (4+房)
+$11684万
+$51,200/呎
+(20年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 662呎 (1房)
 $2895万
@@ -42760,10 +42797,10 @@
 (19年-05月-27日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 908呎 (3房)
 $2902万
@@ -42771,7 +42808,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
 $2840万
@@ -42779,7 +42816,7 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 834呎 (3房)
 $2659万
@@ -42787,43 +42824,6 @@
 (18年-07月-03日)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33&amp;35</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2503呎 (4+房)
-$12510万
-$49,980/呎
-(23年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1624呎 (4+房)
-$8206万
-$50,531/呎
-(20年-03月-23日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 2282呎 (4+房)
-$11684万
-$51,200/呎
-(20年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">

--- a/web/files/港岛-北角-柏蔚山.xlsx
+++ b/web/files/港岛-北角-柏蔚山.xlsx
@@ -38818,10 +38818,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 899呎 (3房)
+$2809万
+$31,244/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 615呎 (2房)
+$2371万
+$38,551/呎
+(19年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 617呎 (2房)
+$2265万
+$36,707/呎
+(19年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 3136呎 (4+房)
 $17716万
@@ -38829,7 +38866,7 @@
 (21年-03月-23日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 2334呎 (4+房)
 $8578万
@@ -38837,7 +38874,7 @@
 (25年-12月-01日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 2375呎 (4+房)
 $11875万
@@ -38845,48 +38882,11 @@
 (19年-11月-20日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
       <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 899呎 (3房)
-$2809万
-$31,244/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 615呎 (2房)
-$2371万
-$38,551/呎
-(19年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>H | 617呎 (2房)
-$2265万
-$36,707/呎
-(19年-07月-09日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -40873,10 +40873,46 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1014呎 (4+房)
+$4398万
+$43,370/呎
+(19年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 1048呎 (4+房)
+$4284万
+$40,874/呎
+(20年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 1075呎 (4+房)
+$3477万
+$32,347/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2058呎 (4+房)
 $10496万
@@ -40884,8 +40920,8 @@
 (20年-04月-01日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1856呎 (4+房)
 $9317万
@@ -40893,8 +40929,8 @@
 (22年-07月-21日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 2028呎 (4+房)
 $10500万
@@ -40902,44 +40938,8 @@
 (21年-03月-10日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1014呎 (4+房)
-$4398万
-$43,370/呎
-(19年-10月-22日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 1048呎 (4+房)
-$4284万
-$40,874/呎
-(20年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 1075呎 (4+房)
-$3477万
-$32,347/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -42748,10 +42748,54 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 662呎 (1房)
+$2895万
+$43,731/呎
+(19年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 908呎 (3房)
+$2902万
+$31,961/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 908呎 (3房)
+$2840万
+$31,278/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 834呎 (3房)
+$2659万
+$31,880/呎
+(18年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>33&amp;35</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2503呎 (4+房)
 $12510万
@@ -42759,8 +42803,8 @@
 (23年-05月-22日)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1624呎 (4+房)
 $8206万
@@ -42768,7 +42812,7 @@
 (20年-03月-23日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 2282呎 (4+房)
 $11684万
@@ -42776,54 +42820,10 @@
 (20年-04月-22日)</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 662呎 (1房)
-$2895万
-$43,731/呎
-(19年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 908呎 (3房)
-$2902万
-$31,961/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 908呎 (3房)
-$2840万
-$31,278/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>H | 834呎 (3房)
-$2659万
-$31,880/呎
-(18年-07月-03日)</t>
-        </is>
-      </c>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">

--- a/web/files/港岛-北角-柏蔚山.xlsx
+++ b/web/files/港岛-北角-柏蔚山.xlsx
@@ -16212,7 +16212,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -41181,7 +41181,7 @@
           <t>A | 1271呎 (4+房)
 $3412万
 $26,843/呎
-(26年-08月-07日)</t>
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
